--- a/3. Attributor and ShapeFileCombiner/ControlFile_AttributorCombiner.xlsx
+++ b/3. Attributor and ShapeFileCombiner/ControlFile_AttributorCombiner.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset\3. Attributor and ShapeFileCombiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8F600C-5831-4F8C-9BE9-F5D04DF92159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1DC299-E677-4F3A-94EB-90E9C7D17092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="-6870" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5190" yWindow="915" windowWidth="14205" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PathsAndNames" sheetId="10" r:id="rId1"/>
@@ -94,7 +94,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B2" authorId="1" shapeId="0" xr:uid="{784EB750-03AA-4950-8508-A908E943EC44}">
+    <comment ref="B2" authorId="1" shapeId="0" xr:uid="{335D2340-E385-48A3-A5DF-DE1825B203C9}">
       <text>
         <r>
           <rPr>
@@ -112,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C2" authorId="2" shapeId="0" xr:uid="{2697B9E9-70FE-4E22-B4E5-0F050E254FFB}">
+    <comment ref="C2" authorId="2" shapeId="0" xr:uid="{4D7DC3A2-4012-4014-8C4C-C33F4E94A8DC}">
       <text>
         <r>
           <rPr>
@@ -129,7 +129,42 @@
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="3" shapeId="0" xr:uid="{E8D8B6FC-D208-4C26-9DD3-64C488BFDF03}">
+    <comment ref="Q2" authorId="1" shapeId="0" xr:uid="{BE46A2EA-203F-48ED-8EA3-E12C772F40F1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Source: https://www.sciencedirect.com/science/article/pii/S0360544222015328
+Converted to USD</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="2" shapeId="0" xr:uid="{F9EFD9FA-D1C7-4724-9A8F-2E8262FFA545}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    IRENA Renewable Power Generation Costs 2022 Table A1.2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="3" shapeId="0" xr:uid="{2261495E-5AAB-4CC2-A5B7-E8F409790734}">
       <text>
         <r>
           <rPr>
@@ -146,7 +181,41 @@
         </r>
       </text>
     </comment>
-    <comment ref="C5" authorId="4" shapeId="0" xr:uid="{0C1E3E75-C2FB-4C21-991D-1F20F344A929}">
+    <comment ref="C5" authorId="4" shapeId="0" xr:uid="{B8FA48B7-2C4F-4B30-87E1-6433C4442FFD}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    IRENA Renewable Power Generation Costs 2022 Table A1.2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q5" authorId="3" shapeId="0" xr:uid="{E6C0405F-044E-45A0-B4CB-61C553551EC5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    From IRENA Renewable Power Generation Costs 2022</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R5" authorId="4" shapeId="0" xr:uid="{1FA04256-79E6-4F72-90E4-97C5D5615EEE}">
       <text>
         <r>
           <rPr>
@@ -168,7 +237,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
     <t>Value</t>
   </si>
@@ -403,18 +472,14 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>\3. Attributor and ShapeFileCombiner\</t>
+      <t>\2. Profile Generator\ControlFile_ProfileGenerator.xlsx</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Results-Prescreen_Bolivia</t>
-    </r>
+  </si>
+  <si>
+    <t>Predefined Gen capital USD/kW</t>
+  </si>
+  <si>
+    <t>Predefined Gen fixed O&amp;M USD/MW/yr</t>
   </si>
   <si>
     <r>
@@ -435,7 +500,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>\2. Profile Generator\ControlFile_ProfileGenerator.xlsx</t>
+      <t>\3. Attributor and ShapeFileCombiner\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Results-Prescreen_Bolivia</t>
     </r>
   </si>
 </sst>
@@ -934,7 +1009,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>37</v>
@@ -945,7 +1020,7 @@
         <v>38</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>26</v>
@@ -1029,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -1050,7 +1125,7 @@
     <col min="16" max="16" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="7" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="7" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1099,8 +1174,14 @@
       <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1152,8 +1233,14 @@
       <c r="P2" s="5">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q2" s="4">
+        <v>1177.2</v>
+      </c>
+      <c r="R2" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1205,8 +1292,14 @@
       <c r="P3" s="5">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q3" s="4">
+        <v>1411.5500000000002</v>
+      </c>
+      <c r="R3" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1258,8 +1351,14 @@
       <c r="P4" s="5">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="4">
+        <v>1520.5500000000002</v>
+      </c>
+      <c r="R4" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1311,8 +1410,14 @@
       <c r="P5" s="5">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="Q5" s="4">
+        <v>876</v>
+      </c>
+      <c r="R5" s="4">
+        <v>17800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
